--- a/ValueSet-pcdch-cytodifferentiation-vs.xlsx
+++ b/ValueSet-pcdch-cytodifferentiation-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2021-11-30T11:37:05-07:00</t>
+    <t>2021-11-30T12:25:27-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-pcdch-cytodifferentiation-vs.xlsx
+++ b/ValueSet-pcdch-cytodifferentiation-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2021-11-30T12:25:27-07:00</t>
+    <t>2021-11-30T14:21:59-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
